--- a/Martinson_Matching_TEMPLATE.xlsx
+++ b/Martinson_Matching_TEMPLATE.xlsx
@@ -129,9 +129,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Responses" displayName="Responses" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
-  <tableColumns count="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Responses" displayName="Responses" ref="A1:O2" headerRowCount="1">
+  <autoFilter ref="A1:O2"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Email"/>
     <tableColumn id="3" name="Class Year"/>
@@ -146,8 +146,7 @@
     <tableColumn id="12" name="Research Areas"/>
     <tableColumn id="13" name="Research Interests"/>
     <tableColumn id="14" name="Fun"/>
-    <tableColumn id="15" name="Issues"/>
-    <tableColumn id="16" name="Anything Else"/>
+    <tableColumn id="15" name="Anything Else"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -442,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,7 +459,6 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,11 +533,6 @@
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Issues</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Anything Else</t>
         </is>
@@ -561,7 +554,6 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
